--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/GEORGIA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/GEORGIA_2020.xlsx
@@ -823,7 +823,7 @@
         <v>14</v>
       </c>
       <c r="D26">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="27">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Montecristo De Guerero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C70">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C109">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C121">
@@ -3145,7 +3145,7 @@
         <v>14</v>
       </c>
       <c r="D155">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="156">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C165">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C189">
@@ -4801,7 +4801,7 @@
         <v>14</v>
       </c>
       <c r="D247">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="248">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C272">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C282">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C291">
@@ -6817,7 +6817,7 @@
         <v>15</v>
       </c>
       <c r="D359">
-        <v>0.0009809050483913157</v>
+        <v>0.0009809050483913155</v>
       </c>
     </row>
     <row r="360">
@@ -6961,7 +6961,7 @@
         <v>15</v>
       </c>
       <c r="D367">
-        <v>0.0009809050483913157</v>
+        <v>0.0009809050483913155</v>
       </c>
     </row>
     <row r="368">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C382">
@@ -7717,7 +7717,7 @@
         <v>14</v>
       </c>
       <c r="D409">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="410">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C444">
@@ -8419,7 +8419,7 @@
         <v>14</v>
       </c>
       <c r="D448">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="449">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C450">
@@ -9751,7 +9751,7 @@
         <v>14</v>
       </c>
       <c r="D522">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="523">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C533">
@@ -11587,7 +11587,7 @@
         <v>14</v>
       </c>
       <c r="D624">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="625">
@@ -11785,7 +11785,7 @@
         <v>14</v>
       </c>
       <c r="D635">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="636">
@@ -12595,7 +12595,7 @@
         <v>15</v>
       </c>
       <c r="D680">
-        <v>0.0009809050483913157</v>
+        <v>0.0009809050483913155</v>
       </c>
     </row>
     <row r="681">
@@ -12883,7 +12883,7 @@
         <v>14</v>
       </c>
       <c r="D696">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="697">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C728">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C740">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C769">
@@ -14712,7 +14712,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C798">
@@ -14917,7 +14917,7 @@
         <v>15</v>
       </c>
       <c r="D809">
-        <v>0.0009809050483913157</v>
+        <v>0.0009809050483913155</v>
       </c>
     </row>
     <row r="810">
@@ -16314,7 +16314,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Yutanduchi De Guerero</t>
+          <t>Yutanduchi De Guerrero</t>
         </is>
       </c>
       <c r="C887">
@@ -17124,7 +17124,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C932">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C990">
@@ -19219,7 +19219,7 @@
         <v>14</v>
       </c>
       <c r="D1048">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1049">
@@ -19561,7 +19561,7 @@
         <v>14</v>
       </c>
       <c r="D1067">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1068">
@@ -20965,7 +20965,7 @@
         <v>14</v>
       </c>
       <c r="D1145">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1146">
@@ -21289,7 +21289,7 @@
         <v>14</v>
       </c>
       <c r="D1163">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1164">
@@ -21847,7 +21847,7 @@
         <v>14</v>
       </c>
       <c r="D1194">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1195">
@@ -22477,7 +22477,7 @@
         <v>14</v>
       </c>
       <c r="D1229">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1230">
@@ -22693,7 +22693,7 @@
         <v>15</v>
       </c>
       <c r="D1241">
-        <v>0.0009809050483913157</v>
+        <v>0.0009809050483913155</v>
       </c>
     </row>
     <row r="1242">
@@ -22981,7 +22981,7 @@
         <v>14</v>
       </c>
       <c r="D1257">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1258">
@@ -24133,7 +24133,7 @@
         <v>14</v>
       </c>
       <c r="D1321">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
     <row r="1322">
@@ -24673,7 +24673,7 @@
         <v>14</v>
       </c>
       <c r="D1351">
-        <v>0.0009155113784985613</v>
+        <v>0.0009155113784985612</v>
       </c>
     </row>
   </sheetData>
